--- a/sample_data/sample_survey_report.xlsx
+++ b/sample_data/sample_survey_report.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 08:03:48</t>
+          <t>2026-06-18 08:23:28</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -556,7 +556,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -586,7 +586,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -601,7 +601,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -616,7 +616,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,7 +631,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -646,7 +646,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -661,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -706,7 +706,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -721,7 +721,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -736,7 +736,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -751,7 +751,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gender=女 | age=nan</t>
+          <t>age=nan | gender=女</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>7 (43.8%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>7 (43.8%)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3305,37 +3305,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>5 (38.5%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (30.8%)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3437,37 +3437,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7 (43.8%)</t>
+          <t>4 (36.4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7 (43.8%)</t>
+          <t>5 (45.5%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -3503,37 +3503,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4 (36.4%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5 (45.5%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>6 (31.6%)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4 (40.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>4 (40.0%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3716,22 +3716,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3 (100.0%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -3767,37 +3767,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5 (38.5%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4 (30.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -3833,37 +3833,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6 (31.6%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3914,22 +3914,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -3965,27 +3965,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>3 (100.0%)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4143,19 +4143,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4165,32 +4165,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (31.2%)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -4221,19 +4221,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4243,32 +4243,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (30.8%)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -4311,42 +4311,42 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -4377,19 +4377,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4399,32 +4399,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5 (31.2%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>6 (54.5%)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -4472,37 +4472,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6 (54.5%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -4555,22 +4555,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5 (50.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -4633,22 +4633,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3 (100.0%)</t>
+          <t>5 (50.0%)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -4689,13 +4689,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -4767,19 +4767,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4789,32 +4789,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>3 (100.0%)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4 (30.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -4862,37 +4862,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>4 (50.0%)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -4923,19 +4923,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4 (50.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5219,7 +5219,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -5244,22 +5244,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (37.5%)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (37.5%)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5295,13 +5295,13 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -5321,27 +5321,27 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (38.5%)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -5367,12 +5367,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -5403,7 +5403,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5465,7 +5465,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5547,7 +5547,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5572,22 +5572,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>6 (37.5%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>5 (45.5%)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>6 (37.5%)</t>
+          <t>4 (36.4%)</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5649,27 +5649,27 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5 (45.5%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>4 (36.4%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5731,27 +5731,27 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>4 (40.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5813,12 +5813,12 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>4 (40.0%)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5951,13 +5951,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5977,27 +5977,27 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>5 (38.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -6059,27 +6059,27 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>4 (50.0%)</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6121,7 +6121,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>4 (50.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6422,12 +6422,12 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>13 (81.2%)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -6461,7 +6461,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6476,12 +6476,12 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>4 (30.8%)</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>9 (69.2%)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -6515,7 +6515,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6530,12 +6530,12 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6638,12 +6638,12 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>4 (36.4%)</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13 (81.2%)</t>
+          <t>7 (63.6%)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6692,12 +6692,12 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>4 (36.4%)</t>
+          <t>8 (42.1%)</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>7 (63.6%)</t>
+          <t>11 (57.9%)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -6731,7 +6731,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6746,12 +6746,12 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>6 (60.0%)</t>
+          <t>2 (100.0%)</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>4 (40.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6800,12 +6800,12 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>6 (60.0%)</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>4 (40.0%)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6854,12 +6854,12 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>8 (100.0%)</t>
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6908,12 +6908,12 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>4 (30.8%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9 (69.2%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6962,12 +6962,12 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>8 (42.1%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>11 (57.9%)</t>
+          <t>7 (87.5%)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -7001,7 +7001,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7016,12 +7016,12 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>8 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -7055,7 +7055,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7070,12 +7070,12 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>7 (87.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -7199,37 +7199,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (37.5%)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7246,7 +7246,7 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
@@ -7269,37 +7269,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7386,7 +7386,7 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="V62" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7479,37 +7479,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>5 (45.5%)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6 (37.5%)</t>
+          <t>3 (27.3%)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7549,37 +7549,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>5 (45.5%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3 (27.3%)</t>
+          <t>6 (31.6%)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>7 (70.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>7 (70.0%)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7759,12 +7759,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7774,22 +7774,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7829,37 +7829,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7899,37 +7899,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6 (31.6%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7969,12 +7969,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7984,22 +7984,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8039,37 +8039,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8241,7 +8241,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8266,17 +8266,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8317,13 +8317,13 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (38.5%)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (46.2%)</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8487,22 +8487,22 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
           <t>1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8569,7 +8569,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>5 (45.5%)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>5 (45.5%)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8656,37 +8656,37 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5 (45.5%)</t>
+          <t>6 (31.6%)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>5 (45.5%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8743,22 +8743,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4 (40.0%)</t>
+          <t>2 (100.0%)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>4 (40.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8825,32 +8825,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>4 (40.0%)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (40.0%)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (62.5%)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8973,13 +8973,13 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>5 (38.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>6 (46.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9066,27 +9066,27 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6 (31.6%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>5 (62.5%)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9143,7 +9143,7 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>5 (62.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9235,32 +9235,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>5 (62.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -9429,7 +9429,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9452,42 +9452,42 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -9519,7 +9519,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (30.8%)</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -9577,17 +9577,17 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -9609,7 +9609,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -9742,32 +9742,32 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
           <t>1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -9789,7 +9789,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9812,52 +9812,52 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>3 (27.3%)</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9902,52 +9902,52 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 (27.3%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -9969,7 +9969,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9997,22 +9997,22 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (100.0%)</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10082,12 +10082,12 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
@@ -10112,22 +10112,22 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -10149,7 +10149,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>gender=女 | age=nan</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -10239,7 +10239,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10257,12 +10257,12 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -10329,7 +10329,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10352,17 +10352,17 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>4 (30.8%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -10419,7 +10419,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10442,27 +10442,27 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -10472,22 +10472,22 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -10509,7 +10509,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -10599,7 +10599,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=nan | gender=女</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -10689,7 +10689,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -10825,7 +10825,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10853,47 +10853,47 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -10915,7 +10915,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10938,37 +10938,37 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>2 (15.4%)</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -11005,7 +11005,7 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -11138,12 +11138,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
           <t>1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -11185,7 +11185,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11213,47 +11213,47 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>3 (27.3%)</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
     </row>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11303,47 +11303,47 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (21.1%)</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>3 (15.8%)</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>3 (27.3%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -11365,7 +11365,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11388,17 +11388,17 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
@@ -11423,17 +11423,17 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>3 (30.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -11455,7 +11455,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11478,17 +11478,17 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
@@ -11508,22 +11508,22 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -11545,7 +11545,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (50.0%)</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>gender=女 | age=nan</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -11635,7 +11635,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -11725,7 +11725,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11748,42 +11748,42 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2 (15.4%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -11815,7 +11815,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11843,47 +11843,47 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>4 (21.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>3 (15.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>4 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -11995,7 +11995,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12023,22 +12023,22 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=nan | gender=女</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -12085,7 +12085,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12103,7 +12103,7 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gender=nan | age=26-35</t>
+          <t>age=18-25 | gender=女</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -12223,7 +12223,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (6.2%)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12248,22 +12248,22 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>6 (37.5%)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (25.0%)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (18.8%)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (12.5%)</t>
         </is>
       </c>
       <c r="S122" t="inlineStr"/>
@@ -12289,19 +12289,19 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>gender=其他 | age=26-35</t>
+          <t>age=18-25 | gender=男</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12326,22 +12326,22 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (38.5%)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>gender=其他 | age=36-45</t>
+          <t>age=26-35 | gender=nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr"/>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>gender=其他 | age=56+</t>
+          <t>age=26-35 | gender=其他</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -12457,7 +12457,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>gender=女 | age=18-25</t>
+          <t>age=26-35 | gender=女</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1 (6.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12555,27 +12555,27 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (18.2%)</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>6 (37.5%)</t>
+          <t>4 (36.4%)</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>4 (25.0%)</t>
+          <t>3 (27.3%)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>3 (18.8%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2 (12.5%)</t>
+          <t>1 (9.1%)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr"/>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>gender=女 | age=26-35</t>
+          <t>age=26-35 | gender=男</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12633,27 +12633,27 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2 (18.2%)</t>
+          <t>1 (5.3%)</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>4 (36.4%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>3 (27.3%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>2 (10.5%)</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>1 (9.1%)</t>
+          <t>5 (26.3%)</t>
         </is>
       </c>
       <c r="S127" t="inlineStr"/>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>gender=女 | age=36-45</t>
+          <t>age=36-45 | gender=其他</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12711,27 +12711,27 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>1 (10.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2 (20.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>5 (50.0%)</t>
+          <t>1 (50.0%)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>gender=女 | age=46-55</t>
+          <t>age=36-45 | gender=女</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -12789,27 +12789,27 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (10.0%)</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (20.0%)</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>3 (100.0%)</t>
+          <t>5 (50.0%)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>gender=女 | age=56+</t>
+          <t>age=36-45 | gender=男</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -12872,22 +12872,22 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2 (66.7%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>1 (33.3%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr"/>
@@ -12913,19 +12913,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>gender=男 | age=18-25</t>
+          <t>age=46-55 | gender=女</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -12960,12 +12960,12 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>5 (38.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>3 (100.0%)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>gender=男 | age=26-35</t>
+          <t>age=46-55 | gender=男</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13023,27 +13023,27 @@
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>1 (5.3%)</t>
+          <t>1 (12.5%)</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>3 (37.5%)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2 (10.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>5 (26.3%)</t>
+          <t>2 (25.0%)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr"/>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>gender=男 | age=36-45</t>
+          <t>age=56+ | gender=其他</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -13081,7 +13081,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13106,22 +13106,22 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr"/>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>gender=男 | age=46-55</t>
+          <t>age=56+ | gender=女</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13179,17 +13179,17 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>1 (12.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>3 (37.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2 (25.0%)</t>
+          <t>1 (33.3%)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr"/>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>gender=男 | age=56+</t>
+          <t>age=56+ | gender=男</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>作答时长仅 41 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 41 秒（低于 120 秒阈值）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>作答时长仅 41 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 41 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>作答时长仅 24 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 24 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>作答时长仅 45 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 45 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>作答时长仅 28 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 28 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>作答时长仅 10 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 10 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>作答时长仅 0 秒（低于 60 秒阈值）</t>
+          <t>作答时长仅 0 秒（低于 120 秒阈值）</t>
         </is>
       </c>
     </row>
